--- a/docs/kanji_n3.xlsx
+++ b/docs/kanji_n3.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IG24-253\Documents\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ADA740-41DE-4C54-ABA0-29CAAB0490D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>Kanji</t>
   </si>
@@ -170,17 +171,143 @@
   <si>
     <t>n3_manage.png</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>筋トレ</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>料理</t>
+  </si>
+  <si>
+    <t>趣味</t>
+  </si>
+  <si>
+    <t>空港</t>
+  </si>
+  <si>
+    <t>筋肉</t>
+  </si>
+  <si>
+    <t>夢</t>
+  </si>
+  <si>
+    <t>目標</t>
+  </si>
+  <si>
+    <t>映像</t>
+  </si>
+  <si>
+    <t>動画</t>
+  </si>
+  <si>
+    <t>心</t>
+  </si>
+  <si>
+    <t>力</t>
+  </si>
+  <si>
+    <t>希望</t>
+  </si>
+  <si>
+    <t>きんトレ</t>
+  </si>
+  <si>
+    <t>しゃしん</t>
+  </si>
+  <si>
+    <t>りょうり</t>
+  </si>
+  <si>
+    <t>しゅみ</t>
+  </si>
+  <si>
+    <t>くうこう</t>
+  </si>
+  <si>
+    <t>きんにく</t>
+  </si>
+  <si>
+    <t>ゆめ</t>
+  </si>
+  <si>
+    <t>もくひょう</t>
+  </si>
+  <si>
+    <t>えいぞう</t>
+  </si>
+  <si>
+    <t>どうが</t>
+  </si>
+  <si>
+    <t>こころ</t>
+  </si>
+  <si>
+    <t>ちから</t>
+  </si>
+  <si>
+    <t>きぼう</t>
+  </si>
+  <si>
+    <t>muscle training/workout</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>cooking</t>
+  </si>
+  <si>
+    <t>hobby</t>
+  </si>
+  <si>
+    <t>airport</t>
+  </si>
+  <si>
+    <t>muscle</t>
+  </si>
+  <si>
+    <t>dream</t>
+  </si>
+  <si>
+    <t>goal</t>
+  </si>
+  <si>
+    <t>video/image</t>
+  </si>
+  <si>
+    <t>video clip</t>
+  </si>
+  <si>
+    <t>heart/mind</t>
+  </si>
+  <si>
+    <t>strength/power</t>
+  </si>
+  <si>
+    <t>hope</t>
+  </si>
+  <si>
+    <t>友達</t>
+  </si>
+  <si>
+    <t>ともだち</t>
+  </si>
+  <si>
+    <t>friend</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -188,13 +315,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -242,7 +369,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -258,9 +385,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -298,9 +425,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -335,7 +462,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -370,7 +497,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -543,11 +670,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -561,7 +688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -575,7 +702,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -589,7 +716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -603,7 +730,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -617,7 +744,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -631,7 +758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -645,7 +772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -659,7 +786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -673,7 +800,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -687,7 +814,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -699,6 +826,160 @@
       </c>
       <c r="D11" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n3.xlsx
+++ b/docs/kanji_n3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ubuntu_practice\java\spring_boot\khans_kanji_english_practice\public\docs\temp_kanjis_to_add\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ADA740-41DE-4C54-ABA0-29CAAB0490D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17D372D-492D-44B7-943E-622D0DD3EEA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="214">
   <si>
     <t>Kanji</t>
   </si>
@@ -297,6 +297,393 @@
   </si>
   <si>
     <t>friend</t>
+  </si>
+  <si>
+    <t>成る</t>
+  </si>
+  <si>
+    <t>若い</t>
+  </si>
+  <si>
+    <t>反対</t>
+  </si>
+  <si>
+    <t>昨日</t>
+  </si>
+  <si>
+    <t>一軒</t>
+  </si>
+  <si>
+    <t>笑う</t>
+  </si>
+  <si>
+    <t>笑顔</t>
+  </si>
+  <si>
+    <t>背中</t>
+  </si>
+  <si>
+    <t>息</t>
+  </si>
+  <si>
+    <t>息子</t>
+  </si>
+  <si>
+    <t>居眠り</t>
+  </si>
+  <si>
+    <t>疲れる</t>
+  </si>
+  <si>
+    <t>胸</t>
+  </si>
+  <si>
+    <t>舟</t>
+  </si>
+  <si>
+    <t>貧しい</t>
+  </si>
+  <si>
+    <t>昔</t>
+  </si>
+  <si>
+    <t>泣く</t>
+  </si>
+  <si>
+    <t>咲く</t>
+  </si>
+  <si>
+    <t>司会</t>
+  </si>
+  <si>
+    <t>残念</t>
+  </si>
+  <si>
+    <t>散らかる</t>
+  </si>
+  <si>
+    <t>怒鳴る</t>
+  </si>
+  <si>
+    <t>怒る</t>
+  </si>
+  <si>
+    <t>才能</t>
+  </si>
+  <si>
+    <t>困難</t>
+  </si>
+  <si>
+    <t>困る</t>
+  </si>
+  <si>
+    <t>大丈夫</t>
+  </si>
+  <si>
+    <t>夫</t>
+  </si>
+  <si>
+    <t>相識</t>
+  </si>
+  <si>
+    <t>狭い</t>
+  </si>
+  <si>
+    <t>抜群</t>
+  </si>
+  <si>
+    <t>群れ</t>
+  </si>
+  <si>
+    <t>祖先</t>
+  </si>
+  <si>
+    <t>隅</t>
+  </si>
+  <si>
+    <t>偶数</t>
+  </si>
+  <si>
+    <t>彼岸</t>
+  </si>
+  <si>
+    <t>彼氏</t>
+  </si>
+  <si>
+    <t>彼女</t>
+  </si>
+  <si>
+    <t>水滴</t>
+  </si>
+  <si>
+    <t>偉大な</t>
+  </si>
+  <si>
+    <t>偉い</t>
+  </si>
+  <si>
+    <t>並木</t>
+  </si>
+  <si>
+    <t>並ぶ</t>
+  </si>
+  <si>
+    <t>なる</t>
+  </si>
+  <si>
+    <t>わかい</t>
+  </si>
+  <si>
+    <t>はんたい</t>
+  </si>
+  <si>
+    <t>きのう</t>
+  </si>
+  <si>
+    <t>いっけん</t>
+  </si>
+  <si>
+    <t>わらう</t>
+  </si>
+  <si>
+    <t>えがお</t>
+  </si>
+  <si>
+    <t>せなか</t>
+  </si>
+  <si>
+    <t>いき</t>
+  </si>
+  <si>
+    <t>むすこ</t>
+  </si>
+  <si>
+    <t>いねむり</t>
+  </si>
+  <si>
+    <t>つかれる</t>
+  </si>
+  <si>
+    <t>むね</t>
+  </si>
+  <si>
+    <t>ふね</t>
+  </si>
+  <si>
+    <t>まずしい</t>
+  </si>
+  <si>
+    <t>むかし</t>
+  </si>
+  <si>
+    <t>なく</t>
+  </si>
+  <si>
+    <t>さく</t>
+  </si>
+  <si>
+    <t>しかい</t>
+  </si>
+  <si>
+    <t>ざんねん</t>
+  </si>
+  <si>
+    <t>ちらかる</t>
+  </si>
+  <si>
+    <t>どなる</t>
+  </si>
+  <si>
+    <t>おこる</t>
+  </si>
+  <si>
+    <t>さいのう</t>
+  </si>
+  <si>
+    <t>こんなん</t>
+  </si>
+  <si>
+    <t>こまる</t>
+  </si>
+  <si>
+    <t>だいじょうぶ</t>
+  </si>
+  <si>
+    <t>おっと</t>
+  </si>
+  <si>
+    <t>そうしき</t>
+  </si>
+  <si>
+    <t>せまい</t>
+  </si>
+  <si>
+    <t>ばつぐん</t>
+  </si>
+  <si>
+    <t>むれ</t>
+  </si>
+  <si>
+    <t>そせん</t>
+  </si>
+  <si>
+    <t>すみ</t>
+  </si>
+  <si>
+    <t>ぐうすう</t>
+  </si>
+  <si>
+    <t>ひがん</t>
+  </si>
+  <si>
+    <t>かれし</t>
+  </si>
+  <si>
+    <t>かのじょ</t>
+  </si>
+  <si>
+    <t>すいてき</t>
+  </si>
+  <si>
+    <t>いだいな</t>
+  </si>
+  <si>
+    <t>えらい</t>
+  </si>
+  <si>
+    <t>なみき</t>
+  </si>
+  <si>
+    <t>ならぶ</t>
+  </si>
+  <si>
+    <t>become</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>opposition</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>one house</t>
+  </si>
+  <si>
+    <t>laugh</t>
+  </si>
+  <si>
+    <t>smiling face</t>
+  </si>
+  <si>
+    <t>back</t>
+  </si>
+  <si>
+    <t>breath</t>
+  </si>
+  <si>
+    <t>son</t>
+  </si>
+  <si>
+    <t>doze</t>
+  </si>
+  <si>
+    <t>be tired</t>
+  </si>
+  <si>
+    <t>chest</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>poor</t>
+  </si>
+  <si>
+    <t>long ago</t>
+  </si>
+  <si>
+    <t>cry</t>
+  </si>
+  <si>
+    <t>bloom</t>
+  </si>
+  <si>
+    <t>master of ceremonies</t>
+  </si>
+  <si>
+    <t>regrettable</t>
+  </si>
+  <si>
+    <t>be messy</t>
+  </si>
+  <si>
+    <t>shout</t>
+  </si>
+  <si>
+    <t>be angry</t>
+  </si>
+  <si>
+    <t>talent</t>
+  </si>
+  <si>
+    <t>difficulty</t>
+  </si>
+  <si>
+    <t>be troubled</t>
+  </si>
+  <si>
+    <t>all right</t>
+  </si>
+  <si>
+    <t>husband</t>
+  </si>
+  <si>
+    <t>acquaintance</t>
+  </si>
+  <si>
+    <t>narrow</t>
+  </si>
+  <si>
+    <t>outstanding</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>ancestor</t>
+  </si>
+  <si>
+    <t>corner</t>
+  </si>
+  <si>
+    <t>even number</t>
+  </si>
+  <si>
+    <t>equinox week</t>
+  </si>
+  <si>
+    <t>boyfriend</t>
+  </si>
+  <si>
+    <t>girlfriend</t>
+  </si>
+  <si>
+    <t>water droplet</t>
+  </si>
+  <si>
+    <t>great</t>
+  </si>
+  <si>
+    <t>great person</t>
+  </si>
+  <si>
+    <t>row of trees</t>
+  </si>
+  <si>
+    <t>line up</t>
   </si>
 </sst>
 </file>
@@ -671,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -980,6 +1367,479 @@
       </c>
       <c r="C25" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B44" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>116</v>
+      </c>
+      <c r="B57" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" t="s">
+        <v>160</v>
+      </c>
+      <c r="C58" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" t="s">
+        <v>161</v>
+      </c>
+      <c r="C59" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" t="s">
+        <v>164</v>
+      </c>
+      <c r="C62" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" t="s">
+        <v>165</v>
+      </c>
+      <c r="C63" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>166</v>
+      </c>
+      <c r="C64" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>167</v>
+      </c>
+      <c r="C65" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C67" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/docs/kanji_n3.xlsx
+++ b/docs/kanji_n3.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652e18b084774022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ac2582d62b7476b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -265,18 +265,12 @@
     <x:t xml:space="preserve">friend</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">成る</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">なる</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">become</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">若い</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">わかい</x:t>
   </x:si>
   <x:si>
@@ -310,9 +304,6 @@
     <x:t xml:space="preserve">one house</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">笑う</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">わらう</x:t>
   </x:si>
   <x:si>
@@ -364,9 +355,6 @@
     <x:t xml:space="preserve">doze</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">疲れる</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">つかれる</x:t>
   </x:si>
   <x:si>
@@ -391,9 +379,6 @@
     <x:t xml:space="preserve">boat</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">貧しい</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">まずしい</x:t>
   </x:si>
   <x:si>
@@ -409,18 +394,12 @@
     <x:t xml:space="preserve">long ago</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">泣く</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">なく</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">cry</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">咲く</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">さく</x:t>
   </x:si>
   <x:si>
@@ -445,9 +424,6 @@
     <x:t xml:space="preserve">regrettable</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">散らかる</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ちらかる</x:t>
   </x:si>
   <x:si>
@@ -463,9 +439,6 @@
     <x:t xml:space="preserve">shout</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">怒る</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">おこる</x:t>
   </x:si>
   <x:si>
@@ -490,9 +463,6 @@
     <x:t xml:space="preserve">difficulty</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">困る</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">こまる</x:t>
   </x:si>
   <x:si>
@@ -526,9 +496,6 @@
     <x:t xml:space="preserve">acquaintance</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">狭い</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">せまい</x:t>
   </x:si>
   <x:si>
@@ -544,9 +511,6 @@
     <x:t xml:space="preserve">outstanding</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">群れ</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">むれ</x:t>
   </x:si>
   <x:si>
@@ -625,9 +589,6 @@
     <x:t xml:space="preserve">great</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">偉い</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">えらい</x:t>
   </x:si>
   <x:si>
@@ -641,9 +602,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">row of trees</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">並ぶ</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ならぶ</x:t>
@@ -1266,476 +1224,476 @@
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="s">
+      <x:c r="A26" t="str">
+        <x:v>成</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B26" t="s">
+      <x:c r="C26" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="C26" t="s">
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>若</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
         <x:v>87</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="s">
+      <x:c r="C27" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B27" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C27" t="s">
-        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B28" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C28" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B29" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C29" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B30" t="s">
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>笑</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C30" t="s">
+      <x:c r="C31" t="s">
         <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B31" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C31" t="s">
-        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C36" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>疲</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B36" t="s">
+      <x:c r="C37" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="C36" t="s">
-        <x:v>117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B37" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C39" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>貧</x:v>
+      </x:c>
+      <x:c r="B40" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C40" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="B39" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B40" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B41" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C41" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>泣</x:v>
+      </x:c>
+      <x:c r="B42" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C42" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>咲</x:v>
+      </x:c>
+      <x:c r="B43" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="B41" t="s">
+      <x:c r="C43" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>132</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B42" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>135</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B43" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="s">
-        <x:v>139</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B44" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C44" t="s">
-        <x:v>141</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="s">
-        <x:v>142</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B45" t="s">
-        <x:v>143</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>144</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" t="s">
-        <x:v>145</x:v>
+      <x:c r="A46" t="str">
+        <x:v>散</x:v>
       </x:c>
       <x:c r="B46" t="s">
-        <x:v>146</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>147</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="s">
-        <x:v>148</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B47" t="s">
-        <x:v>149</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>150</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" t="s">
-        <x:v>151</x:v>
+      <x:c r="A48" t="str">
+        <x:v>怒</x:v>
       </x:c>
       <x:c r="B48" t="s">
-        <x:v>152</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>153</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="s">
-        <x:v>154</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B49" t="s">
-        <x:v>155</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>156</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="s">
-        <x:v>157</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B50" t="s">
-        <x:v>158</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>159</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" t="s">
-        <x:v>160</x:v>
+      <x:c r="A51" t="str">
+        <x:v>困</x:v>
       </x:c>
       <x:c r="B51" t="s">
-        <x:v>161</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>162</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="s">
-        <x:v>163</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B52" t="s">
-        <x:v>164</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>165</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="s">
-        <x:v>166</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B53" t="s">
-        <x:v>167</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C53" t="s">
-        <x:v>168</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="s">
-        <x:v>169</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B54" t="s">
-        <x:v>170</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C54" t="s">
-        <x:v>171</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" t="s">
-        <x:v>172</x:v>
+      <x:c r="A55" t="str">
+        <x:v>狭</x:v>
       </x:c>
       <x:c r="B55" t="s">
-        <x:v>173</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C55" t="s">
-        <x:v>174</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="s">
-        <x:v>175</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B56" t="s">
-        <x:v>176</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C56" t="s">
-        <x:v>177</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" t="s">
-        <x:v>178</x:v>
+      <x:c r="A57" t="str">
+        <x:v>群</x:v>
       </x:c>
       <x:c r="B57" t="s">
-        <x:v>179</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C57" t="s">
-        <x:v>180</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="s">
-        <x:v>181</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B58" t="s">
-        <x:v>182</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C58" t="s">
-        <x:v>183</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="s">
-        <x:v>184</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B59" t="s">
-        <x:v>185</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C59" t="s">
-        <x:v>186</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="s">
-        <x:v>187</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B60" t="s">
-        <x:v>188</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C60" t="s">
-        <x:v>189</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="s">
-        <x:v>190</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B61" t="s">
-        <x:v>191</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C61" t="s">
-        <x:v>192</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="s">
-        <x:v>193</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B62" t="s">
-        <x:v>194</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C62" t="s">
-        <x:v>195</x:v>
+        <x:v>183</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="s">
-        <x:v>196</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B63" t="s">
-        <x:v>197</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C63" t="s">
-        <x:v>198</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="s">
-        <x:v>199</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B64" t="s">
-        <x:v>200</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C64" t="s">
-        <x:v>201</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="s">
-        <x:v>202</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>203</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>204</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" t="s">
-        <x:v>205</x:v>
+      <x:c r="A66" t="str">
+        <x:v>偉</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>206</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>207</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="s">
-        <x:v>208</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>209</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C67" t="s">
-        <x:v>210</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" t="s">
-        <x:v>211</x:v>
+      <x:c r="A68" t="str">
+        <x:v>並</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>212</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C68" t="s">
-        <x:v>213</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1752,7 +1710,7 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="4" t="str">
-        <x:v>盗む</x:v>
+        <x:v>盗</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
         <x:v>ぬすむ</x:v>
@@ -1776,7 +1734,7 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="4" t="str">
-        <x:v>逃げる</x:v>
+        <x:v>逃</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
         <x:v>にげる</x:v>
@@ -1800,7 +1758,7 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="4" t="str">
-        <x:v>疑う</x:v>
+        <x:v>疑</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
         <x:v>うたがう</x:v>
@@ -1812,7 +1770,7 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="4" t="str">
-        <x:v>捕まる</x:v>
+        <x:v>捕</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
         <x:v>つかまる</x:v>
@@ -1836,7 +1794,7 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="4" t="str">
-        <x:v>絶つ</x:v>
+        <x:v>絶</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
         <x:v>たつ</x:v>
@@ -1860,7 +1818,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="4" t="str">
-        <x:v>亡くす</x:v>
+        <x:v>亡</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
         <x:v>なくす</x:v>
@@ -1908,7 +1866,7 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="4" t="str">
-        <x:v>易しい</x:v>
+        <x:v>易</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
         <x:v>やさしい</x:v>
@@ -1956,7 +1914,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="4" t="str">
-        <x:v>敗れる</x:v>
+        <x:v>敗</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
         <x:v>やぶれる</x:v>
@@ -1980,7 +1938,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="4" t="str">
-        <x:v>勝つ</x:v>
+        <x:v>勝</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
         <x:v>かつ</x:v>
@@ -2004,7 +1962,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="4" t="str">
-        <x:v>投げる</x:v>
+        <x:v>投</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
         <x:v>なげる</x:v>
@@ -2028,7 +1986,7 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="4" t="str">
-        <x:v>倒れる</x:v>
+        <x:v>倒</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
         <x:v>たおれる</x:v>
@@ -2040,7 +1998,7 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="4" t="str">
-        <x:v>抱く</x:v>
+        <x:v>抱</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
         <x:v>だく</x:v>
@@ -2064,7 +2022,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="4" t="str">
-        <x:v>怖い</x:v>
+        <x:v>怖</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
         <x:v>こわい</x:v>
@@ -2124,7 +2082,7 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="4" t="str">
-        <x:v>犯す</x:v>
+        <x:v>犯</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
         <x:v>おかす</x:v>
@@ -2148,7 +2106,7 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="4" t="str">
-        <x:v>覚える</x:v>
+        <x:v>覚</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
         <x:v>おぼえる</x:v>
@@ -2184,7 +2142,7 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="4" t="str">
-        <x:v>努める</x:v>
+        <x:v>努</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
         <x:v>つとめる</x:v>
@@ -2208,7 +2166,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="4" t="str">
-        <x:v>求める</x:v>
+        <x:v>求</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
         <x:v>もとめる</x:v>
@@ -2232,7 +2190,7 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="4" t="str">
-        <x:v>許す</x:v>
+        <x:v>許</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
         <x:v>ゆるす</x:v>
@@ -2316,7 +2274,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="4" t="str">
-        <x:v>探す</x:v>
+        <x:v>探</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
         <x:v>さがす</x:v>
@@ -2472,7 +2430,7 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="4" t="str">
-        <x:v>遅い</x:v>
+        <x:v>遅</x:v>
       </x:c>
       <x:c r="B130" s="4" t="str">
         <x:v>おそい</x:v>
@@ -2604,7 +2562,7 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="4" t="str">
-        <x:v>得る</x:v>
+        <x:v>得</x:v>
       </x:c>
       <x:c r="B141" s="4" t="str">
         <x:v>える</x:v>
@@ -2628,7 +2586,7 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="4" t="str">
-        <x:v>告げる</x:v>
+        <x:v>告</x:v>
       </x:c>
       <x:c r="B143" s="4" t="str">
         <x:v>つげる</x:v>
@@ -2724,7 +2682,7 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="4" t="str">
-        <x:v>破る</x:v>
+        <x:v>破</x:v>
       </x:c>
       <x:c r="B151" s="4" t="str">
         <x:v>やぶる</x:v>
@@ -2760,7 +2718,7 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="4" t="str">
-        <x:v>富む</x:v>
+        <x:v>富</x:v>
       </x:c>
       <x:c r="B154" s="4" t="str">
         <x:v>とむ</x:v>
@@ -2928,7 +2886,7 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="4" t="str">
-        <x:v>美しい</x:v>
+        <x:v>美</x:v>
       </x:c>
       <x:c r="B168" s="4" t="str">
         <x:v>うつくしい</x:v>
@@ -3036,7 +2994,7 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="4" t="str">
-        <x:v>苦しい</x:v>
+        <x:v>苦</x:v>
       </x:c>
       <x:c r="B177" s="4" t="str">
         <x:v>くるしい</x:v>
@@ -3120,7 +3078,7 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="4" t="str">
-        <x:v>熱い</x:v>
+        <x:v>熱</x:v>
       </x:c>
       <x:c r="B184" s="4" t="str">
         <x:v>あつい</x:v>
@@ -3144,7 +3102,7 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="4" t="str">
-        <x:v>余る</x:v>
+        <x:v>余</x:v>
       </x:c>
       <x:c r="B186" s="4" t="str">
         <x:v>あまる</x:v>
@@ -3240,7 +3198,7 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="4" t="str">
-        <x:v>痛い</x:v>
+        <x:v>痛</x:v>
       </x:c>
       <x:c r="B194" s="4" t="str">
         <x:v>いたい</x:v>
@@ -3336,7 +3294,7 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="4" t="str">
-        <x:v>訪れる</x:v>
+        <x:v>訪</x:v>
       </x:c>
       <x:c r="B202" s="4" t="str">
         <x:v>おとずれる</x:v>
@@ -3420,7 +3378,7 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="4" t="str">
-        <x:v>辞める</x:v>
+        <x:v>辞</x:v>
       </x:c>
       <x:c r="B209" s="4" t="str">
         <x:v>やめる</x:v>
@@ -3480,7 +3438,7 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="4" t="str">
-        <x:v>頼む</x:v>
+        <x:v>頼</x:v>
       </x:c>
       <x:c r="B214" s="4" t="str">
         <x:v>たのむ</x:v>
@@ -3504,7 +3462,7 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="4" t="str">
-        <x:v>望む</x:v>
+        <x:v>望</x:v>
       </x:c>
       <x:c r="B216" s="4" t="str">
         <x:v>のぞむ</x:v>
@@ -3564,7 +3522,7 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="4" t="str">
-        <x:v>勤める</x:v>
+        <x:v>勤</x:v>
       </x:c>
       <x:c r="B221" s="4" t="str">
         <x:v>つとめる</x:v>
@@ -3612,7 +3570,7 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="4" t="str">
-        <x:v>招く</x:v>
+        <x:v>招</x:v>
       </x:c>
       <x:c r="B225" s="4" t="str">
         <x:v>まねく</x:v>
@@ -3636,7 +3594,7 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="4" t="str">
-        <x:v>欠ける</x:v>
+        <x:v>欠</x:v>
       </x:c>
       <x:c r="B227" s="4" t="str">
         <x:v>かける</x:v>
@@ -3648,7 +3606,7 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="4" t="str">
-        <x:v>喜ぶ</x:v>
+        <x:v>喜</x:v>
       </x:c>
       <x:c r="B228" s="4" t="str">
         <x:v>よろこぶ</x:v>
@@ -3684,7 +3642,7 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="4" t="str">
-        <x:v>治す</x:v>
+        <x:v>治</x:v>
       </x:c>
       <x:c r="B231" s="4" t="str">
         <x:v>なおす</x:v>
@@ -3732,7 +3690,7 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="4" t="str">
-        <x:v>忙しい</x:v>
+        <x:v>忙</x:v>
       </x:c>
       <x:c r="B235" s="4" t="str">
         <x:v>いそがしい</x:v>
@@ -3852,7 +3810,7 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="4" t="str">
-        <x:v>慣れる</x:v>
+        <x:v>慣</x:v>
       </x:c>
       <x:c r="B245" s="4" t="str">
         <x:v>なれる</x:v>
@@ -3912,7 +3870,7 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="4" t="str">
-        <x:v>幸い</x:v>
+        <x:v>幸</x:v>
       </x:c>
       <x:c r="B250" s="4" t="str">
         <x:v>さいわい</x:v>
@@ -3924,7 +3882,7 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="4" t="str">
-        <x:v>失う</x:v>
+        <x:v>失</x:v>
       </x:c>
       <x:c r="B251" s="4" t="str">
         <x:v>うしなう</x:v>
@@ -3984,7 +3942,7 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="4" t="str">
-        <x:v>退く</x:v>
+        <x:v>退</x:v>
       </x:c>
       <x:c r="B256" s="4" t="str">
         <x:v>しりぞく</x:v>
@@ -4032,7 +3990,7 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="4" t="str">
-        <x:v>最も</x:v>
+        <x:v>最</x:v>
       </x:c>
       <x:c r="B260" s="4" t="str">
         <x:v>もっとも</x:v>
@@ -4080,7 +4038,7 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="4" t="str">
-        <x:v>直ちに</x:v>
+        <x:v>直</x:v>
       </x:c>
       <x:c r="B264" s="4" t="str">
         <x:v>ただちに</x:v>
@@ -4104,7 +4062,7 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="4" t="str">
-        <x:v>例えば</x:v>
+        <x:v>例</x:v>
       </x:c>
       <x:c r="B266" s="4" t="str">
         <x:v>たとえば</x:v>
@@ -4140,7 +4098,7 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="4" t="str">
-        <x:v>助かる</x:v>
+        <x:v>助</x:v>
       </x:c>
       <x:c r="B269" s="4" t="str">
         <x:v>たすかる</x:v>
@@ -4188,7 +4146,7 @@
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="4" t="str">
-        <x:v>戦う</x:v>
+        <x:v>戦</x:v>
       </x:c>
       <x:c r="B273" s="4" t="str">
         <x:v>たたかう</x:v>
@@ -4200,7 +4158,7 @@
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="4" t="str">
-        <x:v>争う</x:v>
+        <x:v>争</x:v>
       </x:c>
       <x:c r="B274" s="4" t="str">
         <x:v>あらそう</x:v>
@@ -4224,7 +4182,7 @@
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="4" t="str">
-        <x:v>殺す</x:v>
+        <x:v>殺</x:v>
       </x:c>
       <x:c r="B276" s="4" t="str">
         <x:v>ころす</x:v>
@@ -4248,7 +4206,7 @@
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="4" t="str">
-        <x:v>悲しい</x:v>
+        <x:v>悲</x:v>
       </x:c>
       <x:c r="B278" s="4" t="str">
         <x:v>かなしい</x:v>
@@ -4320,7 +4278,7 @@
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="4" t="str">
-        <x:v>良い</x:v>
+        <x:v>良</x:v>
       </x:c>
       <x:c r="B284" s="4" t="str">
         <x:v>よい</x:v>
@@ -4356,7 +4314,7 @@
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="4" t="str">
-        <x:v>要る</x:v>
+        <x:v>要</x:v>
       </x:c>
       <x:c r="B287" s="4" t="str">
         <x:v>いる</x:v>
@@ -4404,7 +4362,7 @@
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="4" t="str">
-        <x:v>収める</x:v>
+        <x:v>収</x:v>
       </x:c>
       <x:c r="B291" s="4" t="str">
         <x:v>おさめる</x:v>
@@ -4428,7 +4386,7 @@
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="4" t="str">
-        <x:v>連れる</x:v>
+        <x:v>連</x:v>
       </x:c>
       <x:c r="B293" s="4" t="str">
         <x:v>つれる</x:v>
@@ -4452,7 +4410,7 @@
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="4" t="str">
-        <x:v>参る</x:v>
+        <x:v>参</x:v>
       </x:c>
       <x:c r="B295" s="4" t="str">
         <x:v>まいる</x:v>
@@ -4524,7 +4482,7 @@
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="4" t="str">
-        <x:v>配る</x:v>
+        <x:v>配</x:v>
       </x:c>
       <x:c r="B301" s="4" t="str">
         <x:v>くばる</x:v>
@@ -4536,7 +4494,7 @@
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="4" t="str">
-        <x:v>当たる</x:v>
+        <x:v>当</x:v>
       </x:c>
       <x:c r="B302" s="4" t="str">
         <x:v>あたる</x:v>
@@ -4560,7 +4518,7 @@
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="4" t="str">
-        <x:v>頂く</x:v>
+        <x:v>頂</x:v>
       </x:c>
       <x:c r="B304" s="4" t="str">
         <x:v>いただく</x:v>
@@ -4632,7 +4590,7 @@
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="4" t="str">
-        <x:v>全く</x:v>
+        <x:v>全</x:v>
       </x:c>
       <x:c r="B310" s="4" t="str">
         <x:v>まったく</x:v>
@@ -4680,7 +4638,7 @@
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="4" t="str">
-        <x:v>忘れる</x:v>
+        <x:v>忘</x:v>
       </x:c>
       <x:c r="B314" s="4" t="str">
         <x:v>わすれる</x:v>
@@ -4716,7 +4674,7 @@
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="4" t="str">
-        <x:v>過ごす</x:v>
+        <x:v>過</x:v>
       </x:c>
       <x:c r="B317" s="4" t="str">
         <x:v>すごす</x:v>
@@ -4740,7 +4698,7 @@
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="4" t="str">
-        <x:v>任せる</x:v>
+        <x:v>任</x:v>
       </x:c>
       <x:c r="B319" s="4" t="str">
         <x:v>まかせる</x:v>
@@ -4752,7 +4710,7 @@
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="4" t="str">
-        <x:v>負ける</x:v>
+        <x:v>負</x:v>
       </x:c>
       <x:c r="B320" s="4" t="str">
         <x:v>まける</x:v>
@@ -4764,7 +4722,7 @@
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="4" t="str">
-        <x:v>必ず</x:v>
+        <x:v>必</x:v>
       </x:c>
       <x:c r="B321" s="4" t="str">
         <x:v>かならず</x:v>
@@ -4788,7 +4746,7 @@
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="4" t="str">
-        <x:v>積む</x:v>
+        <x:v>積</x:v>
       </x:c>
       <x:c r="B323" s="4" t="str">
         <x:v>つむ</x:v>
@@ -4836,7 +4794,7 @@
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="4" t="str">
-        <x:v>加える</x:v>
+        <x:v>加</x:v>
       </x:c>
       <x:c r="B327" s="4" t="str">
         <x:v>くわえる</x:v>
@@ -4872,7 +4830,7 @@
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="4" t="str">
-        <x:v>記す</x:v>
+        <x:v>記</x:v>
       </x:c>
       <x:c r="B330" s="4" t="str">
         <x:v>しるす</x:v>
@@ -4884,7 +4842,7 @@
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="4" t="str">
-        <x:v>迷う</x:v>
+        <x:v>迷</x:v>
       </x:c>
       <x:c r="B331" s="4" t="str">
         <x:v>まよう</x:v>
@@ -4956,7 +4914,7 @@
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="4" t="str">
-        <x:v>平ら</x:v>
+        <x:v>平</x:v>
       </x:c>
       <x:c r="B337" s="4" t="str">
         <x:v>たいら</x:v>
@@ -4968,7 +4926,7 @@
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="4" t="str">
-        <x:v>果たす</x:v>
+        <x:v>果</x:v>
       </x:c>
       <x:c r="B338" s="4" t="str">
         <x:v>はたす</x:v>
@@ -5028,7 +4986,7 @@
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="4" t="str">
-        <x:v>務める</x:v>
+        <x:v>務</x:v>
       </x:c>
       <x:c r="B343" s="4" t="str">
         <x:v>つとめる</x:v>
@@ -5112,7 +5070,7 @@
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="4" t="str">
-        <x:v>調べる</x:v>
+        <x:v>調</x:v>
       </x:c>
       <x:c r="B350" s="4" t="str">
         <x:v>しらべる</x:v>
@@ -5172,7 +5130,7 @@
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="4" t="str">
-        <x:v>現れる</x:v>
+        <x:v>現</x:v>
       </x:c>
       <x:c r="B355" s="4" t="str">
         <x:v>あらわれる</x:v>
@@ -5184,7 +5142,7 @@
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="4" t="str">
-        <x:v>支える</x:v>
+        <x:v>支</x:v>
       </x:c>
       <x:c r="B356" s="4" t="str">
         <x:v>ささえる</x:v>
@@ -5280,7 +5238,7 @@
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="4" t="str">
-        <x:v>消える</x:v>
+        <x:v>消</x:v>
       </x:c>
       <x:c r="B364" s="4" t="str">
         <x:v>きえる</x:v>
@@ -5304,7 +5262,7 @@
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="4" t="str">
-        <x:v>冷たい</x:v>
+        <x:v>冷</x:v>
       </x:c>
       <x:c r="B366" s="4" t="str">
         <x:v>つめたい</x:v>
@@ -5328,7 +5286,7 @@
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="4" t="str">
-        <x:v>返す</x:v>
+        <x:v>返</x:v>
       </x:c>
       <x:c r="B368" s="4" t="str">
         <x:v>かえす</x:v>
@@ -5376,7 +5334,7 @@
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="4" t="str">
-        <x:v>満ちる</x:v>
+        <x:v>満</x:v>
       </x:c>
       <x:c r="B372" s="4" t="str">
         <x:v>みちる</x:v>
@@ -5424,7 +5382,7 @@
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="4" t="str">
-        <x:v>向こう</x:v>
+        <x:v>向</x:v>
       </x:c>
       <x:c r="B376" s="4" t="str">
         <x:v>むこう</x:v>
@@ -5436,7 +5394,7 @@
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="4" t="str">
-        <x:v>除く</x:v>
+        <x:v>除</x:v>
       </x:c>
       <x:c r="B377" s="4" t="str">
         <x:v>のぞく</x:v>
@@ -5496,7 +5454,7 @@
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="4" t="str">
-        <x:v>守る</x:v>
+        <x:v>守</x:v>
       </x:c>
       <x:c r="B382" s="4" t="str">
         <x:v>まもる</x:v>
@@ -5568,7 +5526,7 @@
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="4" t="str">
-        <x:v>変わる</x:v>
+        <x:v>変</x:v>
       </x:c>
       <x:c r="B388" s="4" t="str">
         <x:v>かわる</x:v>
@@ -5580,7 +5538,7 @@
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="4" t="str">
-        <x:v>選ぶ</x:v>
+        <x:v>選</x:v>
       </x:c>
       <x:c r="B389" s="4" t="str">
         <x:v>えらぶ</x:v>
@@ -5604,7 +5562,7 @@
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="4" t="str">
-        <x:v>決める</x:v>
+        <x:v>決</x:v>
       </x:c>
       <x:c r="B391" s="4" t="str">
         <x:v>きめる</x:v>
@@ -5688,7 +5646,7 @@
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="4" t="str">
-        <x:v>静か</x:v>
+        <x:v>静</x:v>
       </x:c>
       <x:c r="B398" s="4" t="str">
         <x:v>しずか</x:v>
@@ -5712,7 +5670,7 @@
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="4" t="str">
-        <x:v>危ない</x:v>
+        <x:v>危</x:v>
       </x:c>
       <x:c r="B400" s="4" t="str">
         <x:v>あぶない</x:v>
@@ -5724,7 +5682,7 @@
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="4" t="str">
-        <x:v>険しい</x:v>
+        <x:v>険</x:v>
       </x:c>
       <x:c r="B401" s="4" t="str">
         <x:v>けわしい</x:v>
@@ -5748,7 +5706,7 @@
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="4" t="str">
-        <x:v>関わる</x:v>
+        <x:v>関</x:v>
       </x:c>
       <x:c r="B403" s="4" t="str">
         <x:v>かかわる</x:v>
@@ -5784,7 +5742,7 @@
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="4" t="str">
-        <x:v>落ちる</x:v>
+        <x:v>落</x:v>
       </x:c>
       <x:c r="B406" s="4" t="str">
         <x:v>おちる</x:v>
@@ -5808,7 +5766,7 @@
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="4" t="str">
-        <x:v>飛ぶ</x:v>
+        <x:v>飛</x:v>
       </x:c>
       <x:c r="B408" s="4" t="str">
         <x:v>とぶ</x:v>
@@ -5832,7 +5790,7 @@
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="4" t="str">
-        <x:v>遊ぶ</x:v>
+        <x:v>遊</x:v>
       </x:c>
       <x:c r="B410" s="4" t="str">
         <x:v>あそぶ</x:v>
@@ -5844,7 +5802,7 @@
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="4" t="str">
-        <x:v>泳ぐ</x:v>
+        <x:v>泳</x:v>
       </x:c>
       <x:c r="B411" s="4" t="str">
         <x:v>およぐ</x:v>
@@ -5904,7 +5862,7 @@
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="4" t="str">
-        <x:v>常に</x:v>
+        <x:v>常</x:v>
       </x:c>
       <x:c r="B416" s="4" t="str">
         <x:v>つねに</x:v>
@@ -6012,7 +5970,7 @@
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="4" t="str">
-        <x:v>放す</x:v>
+        <x:v>放</x:v>
       </x:c>
       <x:c r="B425" s="4" t="str">
         <x:v>はなす</x:v>
@@ -6024,7 +5982,7 @@
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="4" t="str">
-        <x:v>押す</x:v>
+        <x:v>押</x:v>
       </x:c>
       <x:c r="B426" s="4" t="str">
         <x:v>おす</x:v>
@@ -6108,7 +6066,7 @@
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="4" t="str">
-        <x:v>刻む</x:v>
+        <x:v>刻</x:v>
       </x:c>
       <x:c r="B433" s="4" t="str">
         <x:v>きざむ</x:v>
@@ -6132,7 +6090,7 @@
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="4" t="str">
-        <x:v>速い</x:v>
+        <x:v>速</x:v>
       </x:c>
       <x:c r="B435" s="4" t="str">
         <x:v>はやい</x:v>
@@ -6180,7 +6138,7 @@
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="4" t="str">
-        <x:v>深い</x:v>
+        <x:v>深</x:v>
       </x:c>
       <x:c r="B439" s="4" t="str">
         <x:v>ふかい</x:v>
@@ -6204,7 +6162,7 @@
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="4" t="str">
-        <x:v>降りる</x:v>
+        <x:v>降</x:v>
       </x:c>
       <x:c r="B441" s="4" t="str">
         <x:v>おりる</x:v>
@@ -6264,7 +6222,7 @@
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="4" t="str">
-        <x:v>優しい</x:v>
+        <x:v>優</x:v>
       </x:c>
       <x:c r="B446" s="4" t="str">
         <x:v>やさしい</x:v>
@@ -6312,7 +6270,7 @@
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="4" t="str">
-        <x:v>座る♀️</x:v>
+        <x:v>座</x:v>
       </x:c>
       <x:c r="B450" s="4" t="str">
         <x:v>すわる</x:v>
@@ -6360,7 +6318,7 @@
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="4" t="str">
-        <x:v>初めて</x:v>
+        <x:v>初</x:v>
       </x:c>
       <x:c r="B454" s="4" t="str">
         <x:v>はじめて</x:v>
